--- a/RAWDATA/obs_data_corr.xlsx
+++ b/RAWDATA/obs_data_corr.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/a048908_unipi_it/Documents/R/CHRONOS/NEWCODE/RAWDATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{7F96B26D-4C89-49D2-9A1F-850EFCF4B824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{978577A6-D878-4A2F-8241-EFB3E1BAB4AF}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{35AC7661-2FB9-46F6-93AF-A2319C454FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CB0DB43-97C8-4419-BDFB-985406876DAB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{EC0CE6E9-B12A-4A53-B216-735F4D11F5C9}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>Sites</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Fornace Cappuccini</t>
   </si>
   <si>
-    <t>Pian di Calisti</t>
-  </si>
-  <si>
     <t>Savignano sul Panaro</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
     <t>Pulo di Molfetta Fondo Azzolini</t>
   </si>
   <si>
-    <t xml:space="preserve">Balsignano </t>
-  </si>
-  <si>
     <t>Barice Smilcic</t>
   </si>
   <si>
@@ -248,9 +242,6 @@
     <t>Sa Punta</t>
   </si>
   <si>
-    <t>Cuccuru is Arrius</t>
-  </si>
-  <si>
     <t>Pienza</t>
   </si>
   <si>
@@ -285,6 +276,18 @@
   </si>
   <si>
     <t>Rocchicella-Paliké</t>
+  </si>
+  <si>
+    <t>Balsignano I</t>
+  </si>
+  <si>
+    <t>Balsignano II</t>
+  </si>
+  <si>
+    <t>La Farigoule 2</t>
+  </si>
+  <si>
+    <t>Piani di Calisti</t>
   </si>
 </sst>
 </file>
@@ -1170,14 +1173,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB4B317-EA18-4A42-9CE8-7E9E60090B25}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="8.81640625" style="6"/>
     <col min="2" max="2" width="25.1796875" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="8" width="8.7265625" style="1"/>
+    <col min="5" max="8" width="8.81640625" style="1"/>
     <col min="9" max="9" width="16.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.1796875" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -1200,22 +1203,22 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -1223,7 +1226,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1">
         <v>18.479800000000001</v>
@@ -1293,7 +1296,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1">
         <v>17.619800000000001</v>
@@ -1398,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1">
         <v>17.083549999999999</v>
@@ -1433,7 +1436,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C8" s="4">
         <v>16.875664</v>
@@ -1445,30 +1448,30 @@
         <v>119</v>
       </c>
       <c r="F8" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
         <v>2</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>3</v>
-      </c>
       <c r="K8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>56</v>
+      <c r="B9" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C9" s="1">
         <v>16.721499999999999</v>
@@ -1477,25 +1480,25 @@
         <v>41.069600000000001</v>
       </c>
       <c r="E9" s="1">
-        <v>88</v>
-      </c>
-      <c r="F9" s="1">
+        <v>129</v>
+      </c>
+      <c r="F9" s="2">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2">
         <v>17</v>
       </c>
-      <c r="G9" s="1">
-        <v>15</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>33</v>
-      </c>
-      <c r="K9" s="1">
-        <v>34</v>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>38</v>
+      </c>
+      <c r="K9" s="2">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -1503,34 +1506,34 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1">
-        <v>16.672481999999999</v>
+        <v>16.721499999999999</v>
       </c>
       <c r="D10" s="1">
-        <v>40.674016999999999</v>
+        <v>41.069600000000001</v>
       </c>
       <c r="E10" s="1">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F10" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K10" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -1538,7 +1541,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1">
         <v>16.672481999999999</v>
@@ -1547,13 +1550,13 @@
         <v>40.674016999999999</v>
       </c>
       <c r="E11" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -1562,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K11" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -1573,22 +1576,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1">
-        <v>16.575779000000001</v>
+        <v>16.672481999999999</v>
       </c>
       <c r="D12" s="1">
-        <v>41.194488</v>
+        <v>40.674016999999999</v>
       </c>
       <c r="E12" s="1">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -1597,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K12" s="1">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -1608,19 +1611,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1">
-        <v>16.5336</v>
+        <v>16.575779000000001</v>
       </c>
       <c r="D13" s="1">
-        <v>40.6693</v>
+        <v>41.194488</v>
       </c>
       <c r="E13" s="1">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="F13" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
@@ -1632,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K13" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -1643,22 +1646,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1">
-        <v>16.516999999999999</v>
+        <v>16.5336</v>
       </c>
       <c r="D14" s="1">
-        <v>42.767000000000003</v>
+        <v>40.6693</v>
       </c>
       <c r="E14" s="1">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -1667,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -1678,22 +1681,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1">
-        <v>16.437459</v>
+        <v>16.516999999999999</v>
       </c>
       <c r="D15" s="1">
-        <v>39.684086000000001</v>
+        <v>42.767000000000003</v>
       </c>
       <c r="E15" s="1">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="F15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -1702,10 +1705,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -1713,34 +1716,34 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1">
-        <v>16.298680000000001</v>
+        <v>16.437459</v>
       </c>
       <c r="D16" s="1">
-        <v>38.835389999999997</v>
+        <v>39.684086000000001</v>
       </c>
       <c r="E16" s="1">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="H16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>215</v>
+        <v>9</v>
       </c>
       <c r="K16" s="1">
-        <v>225</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -1748,34 +1751,34 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
-        <v>16.262599999999999</v>
+        <v>16.298680000000001</v>
       </c>
       <c r="D17" s="1">
-        <v>40.570999999999998</v>
+        <v>38.835389999999997</v>
       </c>
       <c r="E17" s="1">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G17" s="1">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J17" s="1">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="K17" s="1">
-        <v>16</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -1783,34 +1786,34 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C18" s="1">
-        <v>16.157499999999999</v>
+        <v>16.262599999999999</v>
       </c>
       <c r="D18" s="1">
-        <v>39.779899999999998</v>
+        <v>40.570999999999998</v>
       </c>
       <c r="E18" s="1">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="F18" s="1">
         <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K18" s="1">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -1818,7 +1821,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1">
         <v>16.157499999999999</v>
@@ -1827,25 +1830,25 @@
         <v>39.779899999999998</v>
       </c>
       <c r="E19" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F19" s="1">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H19" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1">
         <v>2</v>
       </c>
       <c r="J19" s="1">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="K19" s="1">
-        <v>208</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -1853,34 +1856,34 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1">
-        <v>16.0657</v>
+        <v>16.157499999999999</v>
       </c>
       <c r="D20" s="1">
-        <v>41.2239</v>
+        <v>39.779899999999998</v>
       </c>
       <c r="E20" s="1">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="1">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="K20" s="1">
-        <v>1</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -1888,34 +1891,34 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1">
-        <v>16.049199999999999</v>
+        <v>16.0657</v>
       </c>
       <c r="D21" s="1">
-        <v>43.746099999999998</v>
+        <v>41.2239</v>
       </c>
       <c r="E21" s="1">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F21" s="1">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -1923,34 +1926,34 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="1">
+        <v>16.049199999999999</v>
+      </c>
+      <c r="D22" s="1">
+        <v>43.746099999999998</v>
+      </c>
+      <c r="E22" s="1">
+        <v>105</v>
+      </c>
+      <c r="F22" s="1">
+        <v>49</v>
+      </c>
+      <c r="G22" s="1">
+        <v>18</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3</v>
+      </c>
+      <c r="I22" s="1">
+        <v>3</v>
+      </c>
+      <c r="J22" s="1">
         <v>73</v>
       </c>
-      <c r="C22" s="1">
-        <v>16.029699999999998</v>
-      </c>
-      <c r="D22" s="1">
-        <v>43.860799999999998</v>
-      </c>
-      <c r="E22" s="1">
-        <v>106</v>
-      </c>
-      <c r="F22" s="1">
-        <v>10</v>
-      </c>
-      <c r="G22" s="1">
-        <v>3</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
-        <v>6</v>
-      </c>
-      <c r="J22" s="1">
-        <v>19</v>
-      </c>
       <c r="K22" s="1">
-        <v>19</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -1958,34 +1961,34 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C23" s="1">
-        <v>15.9178</v>
+        <v>16.029699999999998</v>
       </c>
       <c r="D23" s="1">
-        <v>37.9392</v>
+        <v>43.860799999999998</v>
       </c>
       <c r="E23" s="1">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="F23" s="1">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="G23" s="1">
-        <v>374</v>
+        <v>3</v>
       </c>
       <c r="H23" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I23" s="1">
-        <v>160</v>
+        <v>6</v>
       </c>
       <c r="J23" s="1">
-        <v>703</v>
+        <v>19</v>
       </c>
       <c r="K23" s="1">
-        <v>703</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -1993,34 +1996,34 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C24" s="1">
-        <v>15.912000000000001</v>
+        <v>15.9178</v>
       </c>
       <c r="D24" s="1">
-        <v>41.636699999999998</v>
+        <v>37.9392</v>
       </c>
       <c r="E24" s="1">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="F24" s="1">
-        <v>8</v>
+        <v>148</v>
       </c>
       <c r="G24" s="1">
-        <v>2</v>
+        <v>374</v>
       </c>
       <c r="H24" s="1">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I24" s="1">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="J24" s="1">
-        <v>11</v>
+        <v>703</v>
       </c>
       <c r="K24" s="1">
-        <v>11</v>
+        <v>703</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -2028,34 +2031,34 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C25" s="1">
-        <v>15.785299999999999</v>
+        <v>15.912000000000001</v>
       </c>
       <c r="D25" s="1">
-        <v>41.526299999999999</v>
+        <v>41.636699999999998</v>
       </c>
       <c r="E25" s="1">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="F25" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K25" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -2063,34 +2066,34 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C26" s="1">
-        <v>15.750553</v>
+        <v>15.785299999999999</v>
       </c>
       <c r="D26" s="1">
-        <v>41.61289</v>
+        <v>41.526299999999999</v>
       </c>
       <c r="E26" s="1">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F26" s="1">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
       </c>
       <c r="I26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="K26" s="1">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -2098,7 +2101,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1">
         <v>15.750553</v>
@@ -2107,25 +2110,25 @@
         <v>41.61289</v>
       </c>
       <c r="E27" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F27" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G27" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
       </c>
       <c r="I27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K27" s="1">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -2133,34 +2136,34 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="C28" s="1">
-        <v>15.71767</v>
+        <v>15.750553</v>
       </c>
       <c r="D28" s="1">
-        <v>44.166699999999999</v>
+        <v>41.61289</v>
       </c>
       <c r="E28" s="1">
-        <v>118</v>
+        <v>47</v>
       </c>
       <c r="F28" s="1">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
       </c>
       <c r="I28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="1">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="K28" s="1">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -2168,19 +2171,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C29" s="1">
-        <v>15.55</v>
+        <v>15.71767</v>
       </c>
       <c r="D29" s="1">
-        <v>41.38</v>
+        <v>44.166699999999999</v>
       </c>
       <c r="E29" s="1">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -2192,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -2203,22 +2206,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1">
-        <v>15.540967</v>
+        <v>15.55</v>
       </c>
       <c r="D30" s="1">
-        <v>41.452627999999997</v>
+        <v>41.38</v>
       </c>
       <c r="E30" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1">
         <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2227,10 +2230,10 @@
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -2238,22 +2241,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1">
-        <v>15.504</v>
+        <v>15.540967</v>
       </c>
       <c r="D31" s="1">
-        <v>44.526000000000003</v>
+        <v>41.452627999999997</v>
       </c>
       <c r="E31" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F31" s="1">
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2262,10 +2265,10 @@
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -2273,22 +2276,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1">
-        <v>15.417999999999999</v>
+        <v>15.504</v>
       </c>
       <c r="D32" s="1">
-        <v>44.117199999999997</v>
+        <v>44.526000000000003</v>
       </c>
       <c r="E32" s="1">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2303,24 +2306,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="C33" s="1">
-        <v>15.404019999999999</v>
+        <v>15.417999999999999</v>
       </c>
       <c r="D33" s="1">
-        <v>41.439570000000003</v>
+        <v>44.117199999999997</v>
       </c>
       <c r="E33" s="1">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="F33" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2332,33 +2335,33 @@
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C34" s="1">
-        <v>15.34183</v>
+        <v>15.404019999999999</v>
       </c>
       <c r="D34" s="1">
-        <v>41.491543999999998</v>
+        <v>41.439570000000003</v>
       </c>
       <c r="E34" s="1">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F34" s="1">
         <v>5</v>
       </c>
       <c r="G34" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -2367,33 +2370,33 @@
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K34" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35">
-        <v>14.700283000000001</v>
-      </c>
-      <c r="D35">
-        <v>37.332642</v>
+        <v>8</v>
+      </c>
+      <c r="C35" s="1">
+        <v>15.34183</v>
+      </c>
+      <c r="D35" s="1">
+        <v>41.491543999999998</v>
       </c>
       <c r="E35" s="1">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -2408,27 +2411,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="1">
-        <v>14.39301</v>
-      </c>
-      <c r="D36" s="1">
-        <v>42.224980000000002</v>
+        <v>80</v>
+      </c>
+      <c r="C36">
+        <v>14.700283000000001</v>
+      </c>
+      <c r="D36">
+        <v>37.332642</v>
       </c>
       <c r="E36" s="1">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="F36" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -2437,30 +2440,30 @@
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K36" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C37" s="1">
-        <v>14.0832</v>
+        <v>14.39301</v>
       </c>
       <c r="D37" s="1">
-        <v>42.374499999999998</v>
+        <v>42.224980000000002</v>
       </c>
       <c r="E37" s="1">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="F37" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G37" s="1">
         <v>2</v>
@@ -2472,263 +2475,269 @@
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K37" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C38" s="1">
-        <v>13.987246000000001</v>
+        <v>14.0832</v>
       </c>
       <c r="D38" s="1">
-        <v>42.430352999999997</v>
+        <v>42.374499999999998</v>
       </c>
       <c r="E38" s="1">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F38" s="1">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="G38" s="1">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="H38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>128</v>
+        <v>5</v>
       </c>
       <c r="K38" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C39" s="1">
-        <v>13.9621</v>
+        <v>13.987246000000001</v>
       </c>
       <c r="D39" s="1">
-        <v>42.221899999999998</v>
+        <v>42.430352999999997</v>
       </c>
       <c r="E39" s="1">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="G39" s="1">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J39" s="1">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="K39" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C40" s="1">
-        <v>13.95064</v>
+        <v>13.9621</v>
       </c>
       <c r="D40" s="1">
-        <v>44.81915</v>
+        <v>42.221899999999998</v>
       </c>
       <c r="E40" s="1">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F40" s="1">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G40" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K40" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C41" s="1">
-        <v>13.943842999999999</v>
+        <v>13.95064</v>
       </c>
       <c r="D41" s="1">
-        <v>42.342669999999998</v>
+        <v>44.81915</v>
       </c>
       <c r="E41" s="1">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F41" s="1">
-        <v>195</v>
+        <v>14</v>
       </c>
       <c r="G41" s="1">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="H41" s="1">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J41" s="1">
-        <v>382</v>
+        <v>31</v>
       </c>
       <c r="K41" s="1">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C42" s="1">
-        <v>13.7567</v>
+        <v>13.943842999999999</v>
       </c>
       <c r="D42" s="1">
-        <v>41.855800000000002</v>
+        <v>42.342669999999998</v>
       </c>
       <c r="E42" s="1">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="F42" s="1">
-        <v>28</v>
+        <v>307</v>
       </c>
       <c r="G42" s="1">
-        <v>11</v>
+        <v>199</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I42" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J42" s="1">
-        <v>39</v>
+        <v>632</v>
       </c>
       <c r="K42" s="1">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>642</v>
+      </c>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C43" s="1">
-        <v>13.66639</v>
+        <v>13.7567</v>
       </c>
       <c r="D43" s="1">
-        <v>41.953890000000001</v>
+        <v>41.855800000000002</v>
       </c>
       <c r="E43" s="1">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="F43" s="1">
-        <v>745</v>
+        <v>28</v>
       </c>
       <c r="G43" s="1">
-        <v>208</v>
+        <v>11</v>
       </c>
       <c r="H43" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I43" s="1">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>1060</v>
+        <v>39</v>
       </c>
       <c r="K43" s="1">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C44" s="1">
-        <v>13.626537000000001</v>
+        <v>13.66639</v>
       </c>
       <c r="D44" s="1">
-        <v>42.754547000000002</v>
+        <v>41.953890000000001</v>
       </c>
       <c r="E44" s="1">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F44" s="1">
-        <v>6</v>
+        <v>745</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H44" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I44" s="1">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J44" s="1">
-        <v>7</v>
+        <v>1060</v>
       </c>
       <c r="K44" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="1">
         <v>13.626537000000001</v>
@@ -2737,42 +2746,42 @@
         <v>42.754547000000002</v>
       </c>
       <c r="E45" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F45" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C46" s="1">
-        <v>13.612299999999999</v>
+        <v>13.626537000000001</v>
       </c>
       <c r="D46" s="1">
-        <v>41.944099999999999</v>
+        <v>42.754547000000002</v>
       </c>
       <c r="E46" s="1">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -2793,24 +2802,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C47" s="1">
-        <v>13.57343</v>
+        <v>13.612299999999999</v>
       </c>
       <c r="D47" s="1">
-        <v>43.56373</v>
+        <v>41.944099999999999</v>
       </c>
       <c r="E47" s="1">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F47" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
@@ -2822,33 +2831,33 @@
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C48" s="1">
-        <v>13.531877</v>
+        <v>13.57343</v>
       </c>
       <c r="D48" s="1">
-        <v>41.948734000000002</v>
+        <v>43.56373</v>
       </c>
       <c r="E48" s="1">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F48" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -2857,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K48" s="1">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -2868,22 +2877,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C49" s="1">
-        <v>13.05987</v>
+        <v>13.531877</v>
       </c>
       <c r="D49" s="1">
-        <v>43.073520000000002</v>
+        <v>41.948734000000002</v>
       </c>
       <c r="E49" s="1">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F49" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
@@ -2892,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K49" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -2903,23 +2912,23 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" s="1">
+        <v>13.05987</v>
+      </c>
+      <c r="D50" s="1">
+        <v>43.073520000000002</v>
+      </c>
+      <c r="E50" s="1">
         <v>43</v>
       </c>
-      <c r="C50" s="1">
-        <v>12.948956000000001</v>
-      </c>
-      <c r="D50" s="1">
-        <v>43.252200999999999</v>
-      </c>
-      <c r="E50" s="1">
-        <v>53</v>
-      </c>
       <c r="F50" s="1">
+        <v>8</v>
+      </c>
+      <c r="G50" s="1">
         <v>4</v>
       </c>
-      <c r="G50" s="1">
-        <v>2</v>
-      </c>
       <c r="H50" s="1">
         <v>0</v>
       </c>
@@ -2927,10 +2936,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K50" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -2938,22 +2947,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="C51" s="1">
-        <v>12.5106</v>
+        <v>12.948956000000001</v>
       </c>
       <c r="D51" s="1">
-        <v>42.515700000000002</v>
+        <v>43.252200999999999</v>
       </c>
       <c r="E51" s="1">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="F51" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -2962,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K51" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -2973,34 +2982,34 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C52" s="1">
-        <v>12.2745</v>
+        <v>12.5106</v>
       </c>
       <c r="D52" s="1">
-        <v>42.104399999999998</v>
+        <v>42.515700000000002</v>
       </c>
       <c r="E52" s="1">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1">
-        <v>847</v>
+        <v>5</v>
       </c>
       <c r="G52" s="1">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I52" s="1">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>1179</v>
+        <v>5</v>
       </c>
       <c r="K52" s="1">
-        <v>1179</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -3008,34 +3017,34 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C53" s="1">
-        <v>12.086119999999999</v>
+        <v>12.2745</v>
       </c>
       <c r="D53" s="1">
-        <v>43.069180000000003</v>
+        <v>42.104399999999998</v>
       </c>
       <c r="E53" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F53" s="1">
-        <v>5</v>
+        <v>951</v>
       </c>
       <c r="G53" s="1">
-        <v>2</v>
+        <v>288</v>
       </c>
       <c r="H53" s="1">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="I53" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J53" s="1">
-        <v>8</v>
+        <v>1309</v>
       </c>
       <c r="K53" s="1">
-        <v>17</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -3043,34 +3052,34 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="C54" s="1">
-        <v>11.872712</v>
+        <v>12.086119999999999</v>
       </c>
       <c r="D54" s="1">
-        <v>44.283427000000003</v>
+        <v>43.069180000000003</v>
       </c>
       <c r="E54" s="1">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F54" s="1">
-        <v>167</v>
+        <v>5</v>
       </c>
       <c r="G54" s="1">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="H54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54" s="1">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="K54" s="1">
-        <v>349</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -3078,34 +3087,34 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C55" s="1">
-        <v>11.6767</v>
+        <v>11.872712</v>
       </c>
       <c r="D55" s="1">
-        <v>43.078699999999998</v>
+        <v>44.283427000000003</v>
       </c>
       <c r="E55" s="1">
-        <v>117</v>
-      </c>
-      <c r="F55" s="1">
-        <v>5</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="1">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="F55" s="2">
+        <v>167</v>
+      </c>
+      <c r="G55" s="2">
+        <v>113</v>
+      </c>
+      <c r="H55" s="2">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2">
+        <v>25</v>
       </c>
       <c r="J55" s="1">
-        <v>5</v>
+        <v>306</v>
       </c>
       <c r="K55" s="1">
-        <v>5</v>
+        <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -3113,22 +3122,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C56" s="1">
-        <v>11.034610000000001</v>
+        <v>11.6767</v>
       </c>
       <c r="D56" s="1">
-        <v>44.475959000000003</v>
+        <v>43.078699999999998</v>
       </c>
       <c r="E56" s="1">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="F56" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -3137,10 +3146,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K56" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -3148,34 +3157,34 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C57" s="1">
-        <v>10.882182999999999</v>
+        <v>11.034610000000001</v>
       </c>
       <c r="D57" s="1">
-        <v>42.381720000000001</v>
+        <v>44.475959000000003</v>
       </c>
       <c r="E57" s="1">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F57" s="1">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I57" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="K57" s="1">
-        <v>174</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -3183,34 +3192,34 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="C58" s="1">
-        <v>10.823464</v>
+        <v>10.882182999999999</v>
       </c>
       <c r="D58" s="1">
-        <v>44.544106999999997</v>
+        <v>42.381720000000001</v>
       </c>
       <c r="E58" s="1">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F58" s="1">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I58" s="1">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J58" s="1">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="K58" s="1">
-        <v>4</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -3221,31 +3230,31 @@
         <v>53</v>
       </c>
       <c r="C59" s="1">
-        <v>10.361458000000001</v>
+        <v>10.823464</v>
       </c>
       <c r="D59" s="1">
-        <v>43.556578000000002</v>
+        <v>44.544106999999997</v>
       </c>
       <c r="E59" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F59" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G59" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
       </c>
       <c r="I59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K59" s="1">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -3253,34 +3262,34 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C60" s="1">
-        <v>10.0938</v>
+        <v>10.361458000000001</v>
       </c>
       <c r="D60" s="1">
-        <v>42.589640000000003</v>
+        <v>43.556578000000002</v>
       </c>
       <c r="E60" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="G60" s="1">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="H60" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I60" s="1">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="J60" s="1">
-        <v>231</v>
+        <v>24</v>
       </c>
       <c r="K60" s="1">
-        <v>231</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -3288,34 +3297,34 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C61" s="1">
-        <v>10.083299999999999</v>
+        <v>10.0938</v>
       </c>
       <c r="D61" s="1">
-        <v>42.58</v>
+        <v>42.589640000000003</v>
       </c>
       <c r="E61" s="1">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="F61" s="1">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G61" s="1">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="H61" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I61" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J61" s="1">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="K61" s="1">
-        <v>295</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -3323,34 +3332,34 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C62" s="1">
-        <v>9.3773800000000005</v>
+        <v>10.083299999999999</v>
       </c>
       <c r="D62" s="1">
-        <v>42.68974</v>
+        <v>42.58</v>
       </c>
       <c r="E62" s="1">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F62" s="1">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="G62" s="1">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="H62" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62" s="1">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="J62" s="1">
-        <v>117</v>
+        <v>282</v>
       </c>
       <c r="K62" s="1">
-        <v>117</v>
+        <v>295</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -3358,34 +3367,34 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C63" s="1">
-        <v>8.9739000000000004</v>
+        <v>9.3773800000000005</v>
       </c>
       <c r="D63" s="1">
-        <v>42.331299999999999</v>
+        <v>42.68974</v>
       </c>
       <c r="E63" s="1">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="F63" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="1">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="J63" s="1">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="K63" s="1">
-        <v>1</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -3393,31 +3402,34 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C64" s="1">
-        <v>8.9212659999999993</v>
+        <v>8.9739000000000004</v>
       </c>
       <c r="D64" s="1">
-        <v>41.526646999999997</v>
+        <v>42.331299999999999</v>
       </c>
       <c r="E64" s="1">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="F64" s="1">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G64" s="1">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
       </c>
       <c r="I64" s="1">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>653</v>
+        <v>1</v>
+      </c>
+      <c r="K64" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -3425,34 +3437,34 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C65" s="1">
-        <v>8.7985299999999995</v>
+        <v>8.9212659999999993</v>
       </c>
       <c r="D65" s="1">
-        <v>41.72871</v>
+        <v>41.526646999999997</v>
       </c>
       <c r="E65" s="1">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="F65" s="1">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="G65" s="1">
-        <v>3</v>
+        <v>555</v>
       </c>
       <c r="H65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>26</v>
+        <v>607</v>
       </c>
       <c r="K65" s="1">
-        <v>26</v>
+        <v>653</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -3460,31 +3472,34 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="C66" s="1">
-        <v>8.5597989999999999</v>
+        <v>8.7985299999999995</v>
       </c>
       <c r="D66" s="1">
-        <v>39.207134000000003</v>
+        <v>41.72871</v>
       </c>
       <c r="E66" s="1">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="G66" s="1">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H66" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I66" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J66" s="1">
-        <v>84</v>
+        <v>26</v>
+      </c>
+      <c r="K66" s="1">
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -3492,31 +3507,34 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C67" s="1">
-        <v>8.5525300000000009</v>
+        <v>8.5597989999999999</v>
       </c>
       <c r="D67" s="1">
-        <v>39.688226</v>
+        <v>39.207134000000003</v>
       </c>
       <c r="E67" s="1">
+        <v>100</v>
+      </c>
+      <c r="F67" s="1">
+        <v>48</v>
+      </c>
+      <c r="G67" s="1">
+        <v>31</v>
+      </c>
+      <c r="H67" s="1">
+        <v>5</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
+        <v>84</v>
+      </c>
+      <c r="K67" s="1">
         <v>101</v>
-      </c>
-      <c r="F67" s="1">
-        <v>76</v>
-      </c>
-      <c r="G67" s="1">
-        <v>608</v>
-      </c>
-      <c r="H67" s="1">
-        <v>31</v>
-      </c>
-      <c r="I67" s="1">
-        <v>49</v>
-      </c>
-      <c r="J67" s="1">
-        <v>764</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -3524,31 +3542,34 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C68" s="1">
-        <v>8.507104</v>
+        <v>8.5525300000000009</v>
       </c>
       <c r="D68" s="1">
-        <v>39.720056</v>
+        <v>39.688226</v>
       </c>
       <c r="E68" s="1">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="F68" s="1">
-        <v>222</v>
+        <v>76</v>
       </c>
       <c r="G68" s="1">
-        <v>954</v>
+        <v>608</v>
       </c>
       <c r="H68" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I68" s="1">
-        <v>218</v>
+        <v>49</v>
       </c>
       <c r="J68" s="1">
-        <v>1421</v>
+        <v>764</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1047</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -3556,31 +3577,34 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C69" s="1">
-        <v>8.5029950000000003</v>
+        <v>8.507104</v>
       </c>
       <c r="D69" s="1">
-        <v>39.920392</v>
+        <v>39.720056</v>
       </c>
       <c r="E69" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F69" s="1">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="G69" s="1">
-        <v>1981</v>
+        <v>954</v>
       </c>
       <c r="H69" s="1">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I69" s="1">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="J69" s="1">
-        <v>2045</v>
+        <v>1421</v>
+      </c>
+      <c r="K69" s="1">
+        <v>2789</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -3588,7 +3612,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C70" s="1">
         <v>8.3282799999999995</v>
@@ -3612,6 +3636,9 @@
         <v>0</v>
       </c>
       <c r="J70" s="1">
+        <v>21</v>
+      </c>
+      <c r="K70" s="1">
         <v>21</v>
       </c>
     </row>
@@ -3690,7 +3717,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C73" s="1">
         <v>5.6444000000000001</v>
@@ -3788,6 +3815,41 @@
       </c>
       <c r="K75" s="1">
         <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A76" s="6">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="1">
+        <v>4.3122199999999999</v>
+      </c>
+      <c r="D76" s="1">
+        <v>43.756900000000002</v>
+      </c>
+      <c r="E76" s="1">
+        <v>130</v>
+      </c>
+      <c r="F76" s="1">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1">
+        <v>1</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1</v>
+      </c>
+      <c r="J76" s="1">
+        <v>4</v>
+      </c>
+      <c r="K76" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/RAWDATA/obs_data_corr.xlsx
+++ b/RAWDATA/obs_data_corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/a048908_unipi_it/Documents/R/CHRONOS/NEWCODE/RAWDATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{35AC7661-2FB9-46F6-93AF-A2319C454FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CB0DB43-97C8-4419-BDFB-985406876DAB}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{35AC7661-2FB9-46F6-93AF-A2319C454FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D34E470-2366-4D17-ADCF-4AC14F72B57F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{EC0CE6E9-B12A-4A53-B216-735F4D11F5C9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC0CE6E9-B12A-4A53-B216-735F4D11F5C9}"/>
   </bookViews>
   <sheets>
     <sheet name="obs_data_corr" sheetId="1" r:id="rId1"/>
@@ -780,7 +780,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -797,6 +797,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1174,19 +1177,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB4B317-EA18-4A42-9CE8-7E9E60090B25}">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="6"/>
-    <col min="2" max="2" width="25.1796875" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="6"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="8" width="8.81640625" style="1"/>
-    <col min="9" max="9" width="16.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" style="1" customWidth="1"/>
+    <col min="5" max="8" width="8.77734375" style="1"/>
+    <col min="9" max="9" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
@@ -1221,7 +1224,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1256,7 +1259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1291,7 +1294,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1326,7 +1329,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1361,7 +1364,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1396,7 +1399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1431,7 +1434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1466,7 +1469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1501,7 +1504,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -1536,7 +1539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -1571,7 +1574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -1606,7 +1609,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -1641,7 +1644,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -1676,7 +1679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -1711,7 +1714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -1746,7 +1749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -1781,7 +1784,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -1816,7 +1819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -1851,7 +1854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -1886,7 +1889,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -1921,7 +1924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -1956,7 +1959,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -1991,7 +1994,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -2026,7 +2029,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -2096,7 +2099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -2131,7 +2134,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>27</v>
       </c>
@@ -2166,7 +2169,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -2174,10 +2177,10 @@
         <v>71</v>
       </c>
       <c r="C29" s="1">
-        <v>15.71767</v>
+        <v>15.820617</v>
       </c>
       <c r="D29" s="1">
-        <v>44.166699999999999</v>
+        <v>43.94594</v>
       </c>
       <c r="E29" s="1">
         <v>118</v>
@@ -2201,17 +2204,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="7">
         <v>15.55</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="7">
         <v>41.38</v>
       </c>
       <c r="E30" s="1">
@@ -2236,7 +2239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -2271,7 +2274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -2306,7 +2309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -2341,7 +2344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>33</v>
       </c>
@@ -2376,7 +2379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -2411,7 +2414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -2446,7 +2449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>36</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -2516,7 +2519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -2551,7 +2554,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>39</v>
       </c>
@@ -2586,7 +2589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -2621,7 +2624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>41</v>
       </c>
@@ -2662,7 +2665,7 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -2732,7 +2735,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>44</v>
       </c>
@@ -2767,7 +2770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>45</v>
       </c>
@@ -2802,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>46</v>
       </c>
@@ -2837,7 +2840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>47</v>
       </c>
@@ -2872,7 +2875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>48</v>
       </c>
@@ -2907,7 +2910,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>49</v>
       </c>
@@ -2942,7 +2945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>50</v>
       </c>
@@ -2977,7 +2980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>51</v>
       </c>
@@ -3012,7 +3015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>52</v>
       </c>
@@ -3047,7 +3050,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -3082,7 +3085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>54</v>
       </c>
@@ -3117,7 +3120,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
         <v>55</v>
       </c>
@@ -3152,7 +3155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -3187,7 +3190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -3222,7 +3225,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>58</v>
       </c>
@@ -3257,7 +3260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>59</v>
       </c>
@@ -3292,7 +3295,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>60</v>
       </c>
@@ -3327,7 +3330,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>61</v>
       </c>
@@ -3362,7 +3365,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -3397,7 +3400,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
         <v>63</v>
       </c>
@@ -3432,7 +3435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
         <v>64</v>
       </c>
@@ -3467,7 +3470,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
         <v>65</v>
       </c>
@@ -3502,7 +3505,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -3537,7 +3540,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>67</v>
       </c>
@@ -3572,7 +3575,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -3607,7 +3610,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>69</v>
       </c>
@@ -3642,7 +3645,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>70</v>
       </c>
@@ -3677,7 +3680,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
         <v>71</v>
       </c>
@@ -3712,7 +3715,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
         <v>72</v>
       </c>
@@ -3747,7 +3750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
         <v>73</v>
       </c>
@@ -3782,7 +3785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
         <v>74</v>
       </c>
@@ -3817,7 +3820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
         <v>75</v>
       </c>
